--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6613-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6613-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0906ADEF-5197-4594-9774-B5280D8608BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5707FA59-4F42-47E0-9D08-DB27FEDAAA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{4339D595-5AE9-4E7C-8A2D-B21610A2A46F}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{7CB9B428-A614-4255-9C9C-5795AB6D8778}"/>
   </bookViews>
   <sheets>
     <sheet name="6613-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1510,25 +1510,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D09D250-CF89-42F2-9199-350DF69F8D89}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE1AC68-CDA8-4B97-91AB-5624527D0ABD}">
   <dimension ref="A1:R24"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1556,7 +1556,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1586,7 +1586,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1682,7 +1682,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1762,7 +1762,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>6.52</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="51">
         <v>2024</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>6.01</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="49">
         <v>2023</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>8.31</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
         <v>2022</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2021</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="51">
         <v>2020</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="49">
         <v>2019</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="51">
         <v>2018</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="49">
         <v>2017</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2016</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="49" t="s">
         <v>41</v>
       </c>
